--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB3" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">هاتف آخر للمدرسة </t>
+          <t xml:space="preserve">جنسية مدير المدرسة</t>
         </is>
       </c>
       <c r="AC3" s="53"/>

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC10\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC10\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D410F030-DAE7-4F09-8A28-413CF31F3E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D8416DC-214A-45A9-A3B2-088948425BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,29 +17,16 @@
     <sheet name="ورقة2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ورقة1!$A$3:$AU$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">ورقة1!$A$3:$AA$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ورقة1!$A$3:$AW$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">ورقة1!$A$3:$AC$3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,25 +81,6 @@
       <charset val="178"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF00B0F0"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF00B050"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
       <sz val="18"/>
       <color theme="1"/>
       <name val="DecoType Naskh Special"/>
@@ -122,19 +90,6 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFFF0000"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <name val="DecoType Naskh Special"/>
       <charset val="178"/>
     </font>
@@ -152,26 +107,6 @@
       <charset val="178"/>
     </font>
     <font>
-      <b/>
-      <sz val="20"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF00B050"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
       <sz val="18"/>
       <color rgb="FF00B0F0"/>
       <name val="DecoType Naskh Special"/>
@@ -181,38 +116,6 @@
       <b/>
       <sz val="18"/>
       <color rgb="FF00B0F0"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF00B050"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <sz val="22"/>
-      <color theme="1"/>
       <name val="DecoType Naskh Special"/>
       <charset val="178"/>
     </font>
@@ -235,68 +138,14 @@
       <charset val="178"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FF00B0F0"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="9" tint="-0.249977111117893"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFC00000"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FFC00000"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FFC00000"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0070C0"/>
       <name val="DecoType Naskh Special"/>
       <charset val="178"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -327,14 +176,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="22">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -360,47 +203,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="thick">
         <color indexed="64"/>
@@ -449,152 +251,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color indexed="64"/>
       </left>
@@ -608,262 +264,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="12" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="16" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="16" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="13" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -871,207 +338,28 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="31" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="16" fontId="13" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="31" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1079,31 +367,12 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF00FF"/>
+      <color rgb="FFAE027D"/>
       <color rgb="FF00FFFF"/>
     </mruColors>
   </colors>
@@ -1116,10 +385,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1412,238 +677,245 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:LQ3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="51" x14ac:dyDescent="1.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="9" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" style="49" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" style="17" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" style="89" customWidth="1"/>
-    <col min="6" max="6" width="24.7109375" style="39" customWidth="1"/>
-    <col min="7" max="7" width="11" style="8" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" style="8" customWidth="1"/>
-    <col min="9" max="9" width="41.7109375" style="40" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" style="40" customWidth="1"/>
-    <col min="11" max="11" width="19.5703125" style="41" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="41" customWidth="1"/>
-    <col min="13" max="13" width="17.42578125" style="42" customWidth="1"/>
-    <col min="14" max="14" width="17.42578125" style="78" customWidth="1"/>
-    <col min="15" max="15" width="10.28515625" style="8" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" style="8" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="8" customWidth="1"/>
-    <col min="18" max="18" width="9.5703125" style="8" customWidth="1"/>
-    <col min="19" max="19" width="17.7109375" style="8" customWidth="1"/>
-    <col min="20" max="20" width="15.7109375" style="41" customWidth="1"/>
-    <col min="21" max="21" width="11.5703125" style="8" customWidth="1"/>
-    <col min="22" max="22" width="16.28515625" style="8" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="8" customWidth="1"/>
-    <col min="24" max="24" width="11.7109375" style="8" customWidth="1"/>
-    <col min="25" max="25" width="13.7109375" style="8" customWidth="1"/>
-    <col min="26" max="26" width="20" style="8" customWidth="1"/>
-    <col min="27" max="27" width="19.42578125" style="8" customWidth="1"/>
-    <col min="28" max="28" width="19.28515625" style="9" customWidth="1"/>
-    <col min="29" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="8.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" style="17" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" style="26" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" style="8" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="41.7109375" style="9" customWidth="1"/>
+    <col min="10" max="10" width="8" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="9" customWidth="1"/>
+    <col min="12" max="12" width="24" style="10" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="10" customWidth="1"/>
+    <col min="14" max="14" width="17.42578125" style="11" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" style="23" customWidth="1"/>
+    <col min="16" max="16" width="10.28515625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="13.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="9.5703125" style="2" customWidth="1"/>
+    <col min="20" max="20" width="17.7109375" style="2" customWidth="1"/>
+    <col min="21" max="22" width="15.7109375" style="10" customWidth="1"/>
+    <col min="23" max="23" width="11.5703125" style="2" customWidth="1"/>
+    <col min="24" max="24" width="20" style="2" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="11.7109375" style="2" customWidth="1"/>
+    <col min="27" max="27" width="13.7109375" style="2" customWidth="1"/>
+    <col min="28" max="28" width="20" style="2" customWidth="1"/>
+    <col min="29" max="29" width="19.42578125" style="2" customWidth="1"/>
+    <col min="30" max="30" width="19.28515625" style="3" customWidth="1"/>
+    <col min="31" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:329" ht="73.5" customHeight="1" x14ac:dyDescent="1.25">
-      <c r="J1" s="155" t="inlineStr">
+    <row r="1" spans="1:31" ht="73.5" customHeight="1" x14ac:dyDescent="1.25">
+      <c r="E1" s="5"/>
+      <c r="K1" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">قاعدة بيانات معلمي مادة الرياضة المدرسية  للمدارس الخاصة - تعليمية محافظة مسقط
-للعام الدراسي (2025م-2026م)</t>
-        </is>
-      </c>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="156"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="156"/>
-    </row>
-    <row r="2" spans="1:329" ht="51.75" thickBot="1" x14ac:dyDescent="1.3">
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="157"/>
-      <c r="R2" s="157"/>
-      <c r="S2" s="157"/>
-      <c r="V2" s="158" t="inlineStr">
+للعام الدراسي (2026م-2027م)</t>
+        </is>
+      </c>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+    </row>
+    <row r="2" spans="1:31" ht="51.75" thickBot="1" x14ac:dyDescent="1.3">
+      <c r="E2" s="5"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="X2" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">نسخة / نجيب المشايخي </t>
         </is>
       </c>
-      <c r="W2" s="158"/>
-      <c r="Z2" s="158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آخر تحديث /  8 / 12 / 2024م </t>
-        </is>
-      </c>
-      <c r="AA2" s="158"/>
-      <c r="AB2" s="88" t="inlineStr">
+      <c r="Y2" s="33"/>
+      <c r="AB2" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آخر تحديث /  16 / 12/ 2025م </t>
+        </is>
+      </c>
+      <c r="AC2" s="34"/>
+      <c r="AD2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">*</t>
         </is>
       </c>
     </row>
-    <row r="3" spans="1:329" s="18" customFormat="1" ht="39.950000000000003" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="1.3">
-      <c r="A3" s="43" t="inlineStr">
+    <row r="3" spans="1:31" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="1.3">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">الولاية </t>
         </is>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="80" t="inlineStr">
+      <c r="B3" s="16"/>
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">المشرف</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">م</t>
         </is>
       </c>
-      <c r="E3" s="90" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">ب</t>
         </is>
       </c>
-      <c r="F3" s="44" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">المدرسة </t>
         </is>
       </c>
-      <c r="G3" s="45" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">الصفوف </t>
         </is>
       </c>
-      <c r="H3" s="45" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">القوة</t>
         </is>
       </c>
-      <c r="I3" s="73" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">اسم المعلم </t>
         </is>
       </c>
-      <c r="J3" s="69" t="inlineStr">
+      <c r="J3" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مدرجة</t>
+        </is>
+      </c>
+      <c r="K3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">عدد الحصص </t>
         </is>
       </c>
-      <c r="K3" s="44" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">الصفوف التي يدرسها</t>
         </is>
       </c>
-      <c r="L3" s="44" t="inlineStr">
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">ملاحظات</t>
         </is>
       </c>
-      <c r="M3" s="46" t="inlineStr">
+      <c r="N3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">التخصص </t>
         </is>
       </c>
-      <c r="N3" s="71" t="inlineStr">
+      <c r="O3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">الهاتف </t>
         </is>
       </c>
-      <c r="O3" s="28" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">الجنسية </t>
         </is>
       </c>
-      <c r="P3" s="28" t="inlineStr">
+      <c r="Q3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">المؤهل </t>
         </is>
       </c>
-      <c r="Q3" s="28" t="inlineStr">
+      <c r="R3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">الحالة الاجتماعية</t>
         </is>
       </c>
-      <c r="R3" s="28" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">اللغة </t>
         </is>
       </c>
-      <c r="S3" s="28" t="inlineStr">
+      <c r="T3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">اسم مدير المدرسة </t>
         </is>
       </c>
-      <c r="T3" s="44" t="inlineStr">
+      <c r="U3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">الهاتف</t>
         </is>
       </c>
-      <c r="U3" s="28" t="inlineStr">
+      <c r="V3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الجنسية </t>
+        </is>
+      </c>
+      <c r="W3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> المنهاج </t>
         </is>
       </c>
-      <c r="V3" s="28" t="inlineStr">
+      <c r="X3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">التقويم </t>
         </is>
       </c>
-      <c r="W3" s="70" t="inlineStr">
+      <c r="Y3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">رياضة (11)</t>
         </is>
       </c>
-      <c r="X3" s="70" t="inlineStr">
+      <c r="Z3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">رياضة (12)</t>
         </is>
       </c>
-      <c r="Y3" s="28" t="inlineStr">
+      <c r="AA3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">الموفقة على التعيين</t>
         </is>
       </c>
-      <c r="Z3" s="72" t="inlineStr">
+      <c r="AB3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">موقع المدرسة </t>
         </is>
       </c>
-      <c r="AA3" s="72" t="inlineStr">
+      <c r="AC3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">هاتف آخر للمدرسة </t>
         </is>
       </c>
-      <c r="AB3" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">جنسية مدير المدرسة</t>
-        </is>
-      </c>
-      <c r="AC3" s="53"/>
+      <c r="AD3" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">هاتف آخر للمدرسة </t>
+        </is>
+      </c>
+      <c r="AE3" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AU17" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:AW3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="3">
-    <mergeCell ref="J1:S2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="K1:T2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="AB2:AC2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I13 I7:I11">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="34" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -3177,663 +2449,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002D2142F494C06546A54739ED34C3B9FD" ma:contentTypeVersion="45" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0df21777ca1e2799a4fb9317a69a4c4d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5d510fa1-58cf-47a5-b1e8-34eac3aaa520" xmlns:ns4="13d3cd5e-86d7-4d91-bf74-7adde606cf83" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc57c1ce7a0cbc1b344ece2ff47d70a" ns3:_="" ns4:_="">
-    <xsd:import namespace="5d510fa1-58cf-47a5-b1e8-34eac3aaa520"/>
-    <xsd:import namespace="13d3cd5e-86d7-4d91-bf74-7adde606cf83"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:SharingHintHash" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns4:NotebookType" minOccurs="0"/>
-                <xsd:element ref="ns4:FolderType" minOccurs="0"/>
-                <xsd:element ref="ns4:CultureName" minOccurs="0"/>
-                <xsd:element ref="ns4:AppVersion" minOccurs="0"/>
-                <xsd:element ref="ns4:TeamsChannelId" minOccurs="0"/>
-                <xsd:element ref="ns4:Owner" minOccurs="0"/>
-                <xsd:element ref="ns4:Math_Settings" minOccurs="0"/>
-                <xsd:element ref="ns4:DefaultSectionNames" minOccurs="0"/>
-                <xsd:element ref="ns4:Templates" minOccurs="0"/>
-                <xsd:element ref="ns4:Leaders" minOccurs="0"/>
-                <xsd:element ref="ns4:Members" minOccurs="0"/>
-                <xsd:element ref="ns4:Member_Groups" minOccurs="0"/>
-                <xsd:element ref="ns4:Distribution_Groups" minOccurs="0"/>
-                <xsd:element ref="ns4:LMS_Mappings" minOccurs="0"/>
-                <xsd:element ref="ns4:Invited_Leaders" minOccurs="0"/>
-                <xsd:element ref="ns4:Invited_Members" minOccurs="0"/>
-                <xsd:element ref="ns4:Self_Registration_Enabled" minOccurs="0"/>
-                <xsd:element ref="ns4:Has_Leaders_Only_SectionGroup" minOccurs="0"/>
-                <xsd:element ref="ns4:Is_Collaboration_Space_Locked" minOccurs="0"/>
-                <xsd:element ref="ns4:IsNotebookLocked" minOccurs="0"/>
-                <xsd:element ref="ns4:Teams_Channel_Section_Location" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns4:Teachers" minOccurs="0"/>
-                <xsd:element ref="ns4:Students" minOccurs="0"/>
-                <xsd:element ref="ns4:Student_Groups" minOccurs="0"/>
-                <xsd:element ref="ns4:Invited_Teachers" minOccurs="0"/>
-                <xsd:element ref="ns4:Invited_Students" minOccurs="0"/>
-                <xsd:element ref="ns4:Has_Teacher_Only_SectionGroup" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns4:_activity" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceSystemTags" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="5d510fa1-58cf-47a5-b1e8-34eac3aaa520" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="SharingHintHash" ma:index="10" nillable="true" ma:displayName="Sharing Hint Hash" ma:description="" ma:internalName="SharingHintHash" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="13d3cd5e-86d7-4d91-bf74-7adde606cf83" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="16" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="19" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="20" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="NotebookType" ma:index="21" nillable="true" ma:displayName="Notebook Type" ma:internalName="NotebookType">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="FolderType" ma:index="22" nillable="true" ma:displayName="Folder Type" ma:internalName="FolderType">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="CultureName" ma:index="23" nillable="true" ma:displayName="Culture Name" ma:internalName="CultureName">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="AppVersion" ma:index="24" nillable="true" ma:displayName="App Version" ma:internalName="AppVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TeamsChannelId" ma:index="25" nillable="true" ma:displayName="Teams Channel Id" ma:internalName="TeamsChannelId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Owner" ma:index="26" nillable="true" ma:displayName="Owner" ma:internalName="Owner">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:User">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="Math_Settings" ma:index="27" nillable="true" ma:displayName="Math Settings" ma:internalName="Math_Settings">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="DefaultSectionNames" ma:index="28" nillable="true" ma:displayName="Default Section Names" ma:internalName="DefaultSectionNames">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Templates" ma:index="29" nillable="true" ma:displayName="Templates" ma:internalName="Templates">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Leaders" ma:index="30" nillable="true" ma:displayName="Leaders" ma:internalName="Leaders">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="Members" ma:index="31" nillable="true" ma:displayName="Members" ma:internalName="Members">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="Member_Groups" ma:index="32" nillable="true" ma:displayName="Member Groups" ma:internalName="Member_Groups">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="Distribution_Groups" ma:index="33" nillable="true" ma:displayName="Distribution Groups" ma:internalName="Distribution_Groups">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LMS_Mappings" ma:index="34" nillable="true" ma:displayName="LMS Mappings" ma:internalName="LMS_Mappings">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Invited_Leaders" ma:index="35" nillable="true" ma:displayName="Invited Leaders" ma:internalName="Invited_Leaders">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Invited_Members" ma:index="36" nillable="true" ma:displayName="Invited Members" ma:internalName="Invited_Members">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Self_Registration_Enabled" ma:index="37" nillable="true" ma:displayName="Self Registration Enabled" ma:internalName="Self_Registration_Enabled">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Has_Leaders_Only_SectionGroup" ma:index="38" nillable="true" ma:displayName="Has Leaders Only SectionGroup" ma:internalName="Has_Leaders_Only_SectionGroup">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Is_Collaboration_Space_Locked" ma:index="39" nillable="true" ma:displayName="Is Collaboration Space Locked" ma:internalName="Is_Collaboration_Space_Locked">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="IsNotebookLocked" ma:index="40" nillable="true" ma:displayName="Is Notebook Locked" ma:internalName="IsNotebookLocked">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Teams_Channel_Section_Location" ma:index="41" nillable="true" ma:displayName="Teams Channel Section Location" ma:internalName="Teams_Channel_Section_Location">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="42" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Teachers" ma:index="43" nillable="true" ma:displayName="Teachers" ma:internalName="Teachers">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="Students" ma:index="44" nillable="true" ma:displayName="Students" ma:internalName="Students">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="Student_Groups" ma:index="45" nillable="true" ma:displayName="Student Groups" ma:internalName="Student_Groups">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="Invited_Teachers" ma:index="46" nillable="true" ma:displayName="Invited Teachers" ma:internalName="Invited_Teachers">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Invited_Students" ma:index="47" nillable="true" ma:displayName="Invited Students" ma:internalName="Invited_Students">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Has_Teacher_Only_SectionGroup" ma:index="48" nillable="true" ma:displayName="Has Teacher Only SectionGroup" ma:internalName="Has_Teacher_Only_SectionGroup">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="49" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_activity" ma:index="50" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="51" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSystemTags" ma:index="52" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Is_Collaboration_Space_Locked xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <Invited_Leaders xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <Invited_Teachers xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <Invited_Students xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <FolderType xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <Leaders xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Leaders>
-    <Templates xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <Members xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Members>
-    <Has_Teacher_Only_SectionGroup xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <Invited_Members xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <TeamsChannelId xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <Distribution_Groups xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <Teachers xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Member_Groups xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Member_Groups>
-    <Self_Registration_Enabled xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <Has_Leaders_Only_SectionGroup xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <AppVersion xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <LMS_Mappings xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <NotebookType xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <CultureName xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <_activity xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-    <Owner xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Student_Groups xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <Students xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Math_Settings xmlns="13d3cd5e-86d7-4d91-bf74-7adde606cf83" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30D8858C-DE5A-484D-8A59-3B88FBF5D19C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="5d510fa1-58cf-47a5-b1e8-34eac3aaa520"/>
-    <ds:schemaRef ds:uri="13d3cd5e-86d7-4d91-bf74-7adde606cf83"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B8AA7C5-F184-46E3-A577-1A0D07345DD8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="5d510fa1-58cf-47a5-b1e8-34eac3aaa520"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="13d3cd5e-86d7-4d91-bf74-7adde606cf83"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61EE5F3E-926B-4639-9C46-8DA46A04F104}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -26,7 +26,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +144,40 @@
       <name val="DecoType Naskh Special"/>
       <charset val="178"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -177,7 +211,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -259,12 +293,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -361,6 +410,93 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -26,7 +26,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,6 +178,13 @@
       <color theme="1"/>
       <name val="DecoType Naskh Special"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -313,7 +320,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -496,6 +503,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -26,7 +26,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,6 +184,52 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
     </font>
   </fonts>
   <fills count="6">
@@ -320,7 +366,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -521,6 +567,78 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -628,7 +746,7 @@
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:cs typeface="DecoType Naskh Special"/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -26,7 +26,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,52 +185,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <b/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -366,7 +320,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -567,78 +521,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -746,7 +628,7 @@
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
-        <a:cs typeface="DecoType Naskh Special"/>
+        <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -26,7 +26,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,6 +184,52 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
     </font>
   </fonts>
   <fills count="6">
@@ -320,7 +366,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -419,108 +465,180 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -628,7 +746,7 @@
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:cs typeface="DecoType Naskh Special"/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -26,7 +26,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,52 +185,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <b/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -366,7 +320,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -465,180 +419,108 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -746,7 +628,7 @@
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
-        <a:cs typeface="DecoType Naskh Special"/>
+        <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -24,528 +24,8 @@
 </workbook>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="178"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FF00B0F0"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF00B0F0"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <sz val="28"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <sz val="28"/>
-      <color rgb="FF0070C0"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <sz val="28"/>
-      <color rgb="FFFF0000"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF0070C0"/>
-      <name val="DecoType Naskh Special"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="6">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-  </fills>
-  <borders count="8">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="70">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-  </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="عادي" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFFF00FF"/>
-      <color rgb="FFAE027D"/>
-      <color rgb="FF00FFFF"/>
-    </mruColors>
-  </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
-</styleSheet>
+<file path=xl/styles.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac x16r2 xr" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision"><fonts count="31" x14ac:knownFonts="1"><font><sz val="11"/><color theme="1"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><b/><sz val="14"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="14"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="12"/><color rgb="FF000000"/><name val="Calibri"/><family val="2"/></font><font><sz val="16"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><b/><sz val="16"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="16"/><color rgb="FFFF0000"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><b/><sz val="16"/><color rgb="FFFF0000"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="18"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><b/><sz val="18"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="20"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><b/><sz val="20"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="18"/><color rgb="FF00B0F0"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><b/><sz val="18"/><color rgb="FF00B0F0"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="28"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="28"/><color rgb="FF0070C0"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="28"/><color rgb="FFFF0000"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><b/><sz val="16"/><color rgb="FF0070C0"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="16"/><color theme="1"/><name val="DecoType Naskh Special"/><b/></font><font><sz val="20"/><color theme="1"/><name val="DecoType Naskh Special"/><b/></font><font><sz val="18"/><color theme="1"/><name val="DecoType Naskh Special"/><b/></font><font><sz val="20"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><sz val="14"/><color theme="1"/><name val="DecoType Naskh Special"/><b/></font><font><sz val="16"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><sz val="14"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="16"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/><b/></font><font><sz val="16"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="20"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/><b/></font><font><sz val="18"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/><b/></font><font><sz val="20"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="14"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/><b/></font></fonts><fills count="6"><fill><patternFill patternType="none"/></fill><fill><patternFill patternType="gray125"/></fill><fill><patternFill patternType="solid"><fgColor theme="8" tint="0.79998168889431442"/><bgColor indexed="64"/></patternFill></fill><fill><patternFill patternType="solid"><fgColor theme="0"/><bgColor indexed="64"/></patternFill></fill><fill><patternFill patternType="solid"><fgColor rgb="FF00FFFF"/><bgColor indexed="64"/></patternFill></fill><fill><patternFill patternType="solid"><fgColor rgb="FF92D050"/><bgColor indexed="64"/></patternFill></fill></fills><borders count="8"><border><left/><right/><top/><bottom/><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left/><right/><top/><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left/><right style="thick"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right/><top style="thick"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right/><top/><bottom/><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border></borders><cellStyleXfs count="2"><xf numFmtId="0" fontId="0" fillId="0" borderId="0"/><xf numFmtId="0" fontId="3" fillId="0" borderId="0"/></cellStyleXfs><cellXfs count="97"><xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/><xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/><xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment vertical="center"/><xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/><xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment vertical="center"/><xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/><xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="top"/><xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/></cellXfs><cellStyles count="2"><cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/><cellStyle name="عادي" xfId="0" builtinId="0"/></cellStyles><dxfs count="0"/><tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/><colors><mruColors><color rgb="FFFF00FF"/><color rgb="FFAE027D"/><color rgb="FF00FFFF"/></mruColors></colors><extLst><ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main"><x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/></ext><ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main"><x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/></ext></extLst></styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -628,7 +108,7 @@
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:cs typeface="DecoType Naskh Special"/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -24,8 +24,537 @@
 </workbook>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac x16r2 xr" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision"><fonts count="31" x14ac:knownFonts="1"><font><sz val="11"/><color theme="1"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><b/><sz val="14"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="14"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="12"/><color rgb="FF000000"/><name val="Calibri"/><family val="2"/></font><font><sz val="16"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><b/><sz val="16"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="16"/><color rgb="FFFF0000"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><b/><sz val="16"/><color rgb="FFFF0000"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="18"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><b/><sz val="18"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="20"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><b/><sz val="20"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="18"/><color rgb="FF00B0F0"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><b/><sz val="18"/><color rgb="FF00B0F0"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="28"/><color theme="1"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="28"/><color rgb="FF0070C0"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="28"/><color rgb="FFFF0000"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><b/><sz val="16"/><color rgb="FF0070C0"/><name val="DecoType Naskh Special"/><charset val="178"/></font><font><sz val="16"/><color theme="1"/><name val="DecoType Naskh Special"/><b/></font><font><sz val="20"/><color theme="1"/><name val="DecoType Naskh Special"/><b/></font><font><sz val="18"/><color theme="1"/><name val="DecoType Naskh Special"/><b/></font><font><sz val="20"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><sz val="14"/><color theme="1"/><name val="DecoType Naskh Special"/><b/></font><font><sz val="16"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><sz val="14"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="16"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/><b/></font><font><sz val="16"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="20"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/><b/></font><font><sz val="18"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/><b/></font><font><sz val="20"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="14"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/><b/></font></fonts><fills count="6"><fill><patternFill patternType="none"/></fill><fill><patternFill patternType="gray125"/></fill><fill><patternFill patternType="solid"><fgColor theme="8" tint="0.79998168889431442"/><bgColor indexed="64"/></patternFill></fill><fill><patternFill patternType="solid"><fgColor theme="0"/><bgColor indexed="64"/></patternFill></fill><fill><patternFill patternType="solid"><fgColor rgb="FF00FFFF"/><bgColor indexed="64"/></patternFill></fill><fill><patternFill patternType="solid"><fgColor rgb="FF92D050"/><bgColor indexed="64"/></patternFill></fill></fills><borders count="8"><border><left/><right/><top/><bottom/><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left/><right/><top/><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left/><right style="thick"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right/><top style="thick"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right/><top/><bottom/><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border></borders><cellStyleXfs count="2"><xf numFmtId="0" fontId="0" fillId="0" borderId="0"/><xf numFmtId="0" fontId="3" fillId="0" borderId="0"/></cellStyleXfs><cellXfs count="97"><xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/><xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/><xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment vertical="center"/><xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/><xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment vertical="center"/><xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/><xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="top"/><xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/></cellXfs><cellStyles count="2"><cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/><cellStyle name="عادي" xfId="0" builtinId="0"/></cellStyles><dxfs count="0"/><tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/><colors><mruColors><color rgb="FFFF00FF"/><color rgb="FFAE027D"/><color rgb="FF00FFFF"/></mruColors></colors><extLst><ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main"><x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/></ext><ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main"><x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/></ext></extLst></styleSheet>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="25" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF00B0F0"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF00B0F0"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color rgb="FF0070C0"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color rgb="FFFF0000"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF0070C0"/>
+      <name val="DecoType Naskh Special"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="6">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="8">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="73">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="2">
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="عادي" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF00FF"/>
+      <color rgb="FFAE027D"/>
+      <color rgb="FF00FFFF"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -108,7 +637,7 @@
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
-        <a:cs typeface="DecoType Naskh Special"/>
+        <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -39,13 +39,13 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
@@ -57,126 +57,126 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="18"/>
       <color rgb="FF00B0F0"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FF00B0F0"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="28"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="28"/>
       <color rgb="FF0070C0"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="28"/>
       <color rgb="FFFF0000"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF0070C0"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <b/>
     </font>
     <font>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <b/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <b/>
     </font>
     <font>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <b/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <sz val="14"/>

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -39,13 +39,13 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
@@ -57,126 +57,126 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="18"/>
       <color rgb="FF00B0F0"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FF00B0F0"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="28"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="28"/>
       <color rgb="FF0070C0"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="28"/>
       <color rgb="FFFF0000"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF0070C0"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <charset val="178"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <b/>
     </font>
     <font>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <b/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <b/>
     </font>
     <font>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <b/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="14"/>

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -26,7 +26,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,6 +185,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -320,7 +325,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -530,6 +535,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -325,7 +325,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -554,6 +554,27 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -26,7 +26,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,6 +189,23 @@
       <sz val="18"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <b/>
     </font>
   </fonts>
   <fills count="6">
@@ -325,7 +342,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -574,6 +591,15 @@
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
   </cellXfs>

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -920,35 +920,36 @@
   <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="51" x14ac:dyDescent="1.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" style="26" customWidth="1"/>
-    <col min="6" max="6" width="24.7109375" style="8" customWidth="1"/>
-    <col min="7" max="7" width="11" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="41.7109375" style="9" customWidth="1"/>
-    <col min="10" max="10" width="8" style="2" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" style="9" customWidth="1"/>
-    <col min="12" max="12" width="24" style="10" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="10" customWidth="1"/>
-    <col min="14" max="14" width="17.42578125" style="11" customWidth="1"/>
-    <col min="15" max="15" width="17.42578125" style="23" customWidth="1"/>
-    <col min="16" max="16" width="10.28515625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="13.140625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="9.5703125" style="2" customWidth="1"/>
-    <col min="20" max="20" width="17.7109375" style="2" customWidth="1"/>
-    <col min="21" max="22" width="15.7109375" style="10" customWidth="1"/>
-    <col min="23" max="23" width="11.5703125" style="2" customWidth="1"/>
-    <col min="24" max="24" width="20" style="2" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="2" customWidth="1"/>
-    <col min="26" max="26" width="11.7109375" style="2" customWidth="1"/>
-    <col min="27" max="27" width="13.7109375" style="2" customWidth="1"/>
-    <col min="28" max="28" width="20" style="2" customWidth="1"/>
-    <col min="29" max="29" width="19.42578125" style="2" customWidth="1"/>
-    <col min="30" max="30" width="19.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.7" style="3" customWidth="1"/>
+    <col min="2" max="2" width="6.57" style="17" customWidth="1"/>
+    <col min="3" max="3" width="24.3" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.29" style="5" customWidth="1"/>
+    <col min="5" max="5" width="6.29" style="26" customWidth="1"/>
+    <col min="6" max="6" width="36.9" style="8" customWidth="1"/>
+    <col min="7" max="7" width="11.0" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7.71" style="2" customWidth="1"/>
+    <col min="9" max="9" width="60.0" style="9" customWidth="1"/>
+    <col min="10" max="10" width="12.1" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.86" style="9" customWidth="1"/>
+    <col min="12" max="12" width="47.7" style="10" customWidth="1"/>
+    <col min="13" max="13" width="15.57" style="10" customWidth="1"/>
+    <col min="14" max="14" width="60.0" style="11" customWidth="1"/>
+    <col min="15" max="15" width="17.43" style="23" customWidth="1"/>
+    <col min="16" max="16" width="12.1" style="2" customWidth="1"/>
+    <col min="17" max="17" width="59.7" style="2" customWidth="1"/>
+    <col min="18" max="18" width="11.71" style="2" customWidth="1"/>
+    <col min="19" max="19" width="17.8" style="2" customWidth="1"/>
+    <col min="20" max="20" width="32.1" style="2" customWidth="1"/>
+    <col min="21" max="21" width="15.71" style="10" customWidth="1"/>
+    <col min="22" max="22" width="20.1" style="10" customWidth="1"/>
+    <col min="23" max="23" width="21.3" style="2" customWidth="1"/>
+    <col min="24" max="24" width="28.1" style="2" customWidth="1"/>
+    <col min="25" max="25" width="14.57" style="2" customWidth="1"/>
+    <col min="26" max="26" width="12.1" style="2" customWidth="1"/>
+    <col min="27" max="27" width="16.5" style="2" customWidth="1"/>
+    <col min="28" max="28" width="21.3" style="2" customWidth="1"/>
+    <col min="29" max="29" width="19.43" style="2" customWidth="1"/>
+    <col min="30" max="30" width="19.29" style="3" customWidth="1"/>
     <col min="31" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ورقة1!$A$3:$AW$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">ورقة1!$A$3:$AC$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">ورقة1!$A$3:$AD$3</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
 </workbook>
@@ -930,38 +930,107 @@
     <col min="8" max="8" width="7.71" style="2" customWidth="1"/>
     <col min="9" max="9" width="60.0" style="9" customWidth="1"/>
     <col min="10" max="10" width="12.1" style="2" customWidth="1"/>
-    <col min="11" max="11" width="9.86" style="9" customWidth="1"/>
-    <col min="12" max="12" width="47.7" style="10" customWidth="1"/>
-    <col min="13" max="13" width="15.57" style="10" customWidth="1"/>
-    <col min="14" max="14" width="60.0" style="11" customWidth="1"/>
-    <col min="15" max="15" width="17.43" style="23" customWidth="1"/>
-    <col min="16" max="16" width="12.1" style="2" customWidth="1"/>
-    <col min="17" max="17" width="59.7" style="2" customWidth="1"/>
-    <col min="18" max="18" width="11.71" style="2" customWidth="1"/>
-    <col min="19" max="19" width="17.8" style="2" customWidth="1"/>
-    <col min="20" max="20" width="32.1" style="2" customWidth="1"/>
-    <col min="21" max="21" width="15.71" style="10" customWidth="1"/>
-    <col min="22" max="22" width="20.1" style="10" customWidth="1"/>
-    <col min="23" max="23" width="21.3" style="2" customWidth="1"/>
-    <col min="24" max="24" width="28.1" style="2" customWidth="1"/>
-    <col min="25" max="25" width="14.57" style="2" customWidth="1"/>
-    <col min="26" max="26" width="12.1" style="2" customWidth="1"/>
-    <col min="27" max="27" width="16.5" style="2" customWidth="1"/>
-    <col min="28" max="28" width="21.3" style="2" customWidth="1"/>
-    <col min="29" max="29" width="19.43" style="2" customWidth="1"/>
-    <col min="30" max="30" width="19.29" style="3" customWidth="1"/>
-    <col min="31" max="16384" width="9" style="1"/>
+    <col min="11" max="11" width="16.0" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9.86" style="9" customWidth="1"/>
+    <col min="13" max="13" width="47.7" style="10" customWidth="1"/>
+    <col min="14" max="14" width="15.57" style="10" customWidth="1"/>
+    <col min="15" max="15" width="60.0" style="11" customWidth="1"/>
+    <col min="16" max="16" width="17.43" style="23" customWidth="1"/>
+    <col min="17" max="17" width="12.1" style="2" customWidth="1"/>
+    <col min="18" max="18" width="59.7" style="2" customWidth="1"/>
+    <col min="19" max="19" width="11.71" style="2" customWidth="1"/>
+    <col min="20" max="20" width="17.8" style="2" customWidth="1"/>
+    <col min="21" max="21" width="32.1" style="2" customWidth="1"/>
+    <col min="22" max="22" width="15.71" style="10" customWidth="1"/>
+    <col min="23" max="23" width="20.1" style="10" customWidth="1"/>
+    <col min="24" max="24" width="21.3" style="2" customWidth="1"/>
+    <col min="25" max="25" width="28.1" style="2" customWidth="1"/>
+    <col min="26" max="26" width="14.57" style="2" customWidth="1"/>
+    <col min="27" max="27" width="12.1" style="2" customWidth="1"/>
+    <col min="28" max="28" width="16.5" style="2" customWidth="1"/>
+    <col min="29" max="29" width="21.3" style="2" customWidth="1"/>
+    <col min="30" max="30" width="19.43" style="2" customWidth="1"/>
+    <col min="31" max="31" width="19.29" style="3" customWidth="1"/>
+    <col min="32" max="32" width="9" style="1"/>
+    <col min="33" max="33" width="9" style="1"/>
+    <col min="34" max="34" width="9" style="1"/>
+    <col min="35" max="35" width="9" style="1"/>
+    <col min="36" max="36" width="9" style="1"/>
+    <col min="37" max="37" width="9" style="1"/>
+    <col min="38" max="38" width="9" style="1"/>
+    <col min="39" max="39" width="9" style="1"/>
+    <col min="40" max="40" width="9" style="1"/>
+    <col min="41" max="41" width="9" style="1"/>
+    <col min="42" max="42" width="9" style="1"/>
+    <col min="43" max="43" width="9" style="1"/>
+    <col min="44" max="44" width="9" style="1"/>
+    <col min="45" max="45" width="9" style="1"/>
+    <col min="46" max="46" width="9" style="1"/>
+    <col min="47" max="47" width="9" style="1"/>
+    <col min="48" max="48" width="9" style="1"/>
+    <col min="49" max="49" width="9" style="1"/>
+    <col min="50" max="50" width="9" style="1"/>
+    <col min="51" max="51" width="9" style="1"/>
+    <col min="52" max="52" width="9" style="1"/>
+    <col min="53" max="53" width="9" style="1"/>
+    <col min="54" max="54" width="9" style="1"/>
+    <col min="55" max="55" width="9" style="1"/>
+    <col min="56" max="56" width="9" style="1"/>
+    <col min="57" max="57" width="9" style="1"/>
+    <col min="58" max="58" width="9" style="1"/>
+    <col min="59" max="59" width="9" style="1"/>
+    <col min="60" max="60" width="9" style="1"/>
+    <col min="61" max="61" width="9" style="1"/>
+    <col min="62" max="62" width="9" style="1"/>
+    <col min="63" max="63" width="9" style="1"/>
+    <col min="64" max="64" width="9" style="1"/>
+    <col min="65" max="65" width="9" style="1"/>
+    <col min="66" max="66" width="9" style="1"/>
+    <col min="67" max="67" width="9" style="1"/>
+    <col min="68" max="68" width="9" style="1"/>
+    <col min="69" max="69" width="9" style="1"/>
+    <col min="70" max="70" width="9" style="1"/>
+    <col min="71" max="71" width="9" style="1"/>
+    <col min="72" max="72" width="9" style="1"/>
+    <col min="73" max="73" width="9" style="1"/>
+    <col min="74" max="74" width="9" style="1"/>
+    <col min="75" max="75" width="9" style="1"/>
+    <col min="76" max="76" width="9" style="1"/>
+    <col min="77" max="77" width="9" style="1"/>
+    <col min="78" max="78" width="9" style="1"/>
+    <col min="79" max="79" width="9" style="1"/>
+    <col min="80" max="80" width="9" style="1"/>
+    <col min="81" max="81" width="9" style="1"/>
+    <col min="82" max="82" width="9" style="1"/>
+    <col min="83" max="83" width="9" style="1"/>
+    <col min="84" max="84" width="9" style="1"/>
+    <col min="85" max="85" width="9" style="1"/>
+    <col min="86" max="86" width="9" style="1"/>
+    <col min="87" max="87" width="9" style="1"/>
+    <col min="88" max="88" width="9" style="1"/>
+    <col min="89" max="89" width="9" style="1"/>
+    <col min="90" max="90" width="9" style="1"/>
+    <col min="91" max="91" width="9" style="1"/>
+    <col min="92" max="92" width="9" style="1"/>
+    <col min="93" max="93" width="9" style="1"/>
+    <col min="94" max="94" width="9" style="1"/>
+    <col min="95" max="95" width="9" style="1"/>
+    <col min="96" max="96" width="9" style="1"/>
+    <col min="97" max="97" width="9" style="1"/>
+    <col min="98" max="98" width="9" style="1"/>
+    <col min="99" max="99" width="9" style="1"/>
+    <col min="100" max="100" width="9" style="1"/>
+    <col min="101" max="101" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="73.5" customHeight="1" x14ac:dyDescent="1.25">
+    <row r="1" spans="1:32" ht="73.5" customHeight="1" x14ac:dyDescent="1.25">
       <c r="E1" s="5"/>
-      <c r="K1" s="30" t="inlineStr">
+      <c r="L1" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">قاعدة بيانات معلمي مادة الرياضة المدرسية  للمدارس الخاصة - تعليمية محافظة مسقط
 للعام الدراسي (2026م-2027م)</t>
         </is>
       </c>
-      <c r="L1" s="31"/>
       <c r="M1" s="31"/>
       <c r="N1" s="31"/>
       <c r="O1" s="31"/>
@@ -970,10 +1039,10 @@
       <c r="R1" s="31"/>
       <c r="S1" s="31"/>
       <c r="T1" s="31"/>
-    </row>
-    <row r="2" spans="1:31" ht="51.75" thickBot="1" x14ac:dyDescent="1.3">
+      <c r="U1" s="31"/>
+    </row>
+    <row r="2" spans="1:32" ht="51.75" thickBot="1" x14ac:dyDescent="1.3">
       <c r="E2" s="5"/>
-      <c r="K2" s="32"/>
       <c r="L2" s="32"/>
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
@@ -983,25 +1052,26 @@
       <c r="R2" s="32"/>
       <c r="S2" s="32"/>
       <c r="T2" s="32"/>
-      <c r="X2" s="33" t="inlineStr">
+      <c r="U2" s="32"/>
+      <c r="Y2" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">نسخة / نجيب المشايخي </t>
         </is>
       </c>
-      <c r="Y2" s="33"/>
-      <c r="AB2" s="34" t="inlineStr">
+      <c r="Z2" s="33"/>
+      <c r="AC2" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">آخر تحديث /  16 / 12/ 2025م </t>
         </is>
       </c>
-      <c r="AC2" s="34"/>
-      <c r="AD2" s="25" t="inlineStr">
+      <c r="AD2" s="34"/>
+      <c r="AE2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">*</t>
         </is>
       </c>
     </row>
-    <row r="3" spans="1:31" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="1.3">
+    <row r="3" spans="1:32" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="1.3">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">الولاية </t>
@@ -1048,114 +1118,119 @@
           <t xml:space="preserve">مدرجة</t>
         </is>
       </c>
-      <c r="K3" s="28" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">كفالة المدرسة</t>
+        </is>
+      </c>
+      <c r="L3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">عدد الحصص </t>
         </is>
       </c>
-      <c r="L3" s="13" t="inlineStr">
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">الصفوف التي يدرسها</t>
         </is>
       </c>
-      <c r="M3" s="13" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">ملاحظات</t>
         </is>
       </c>
-      <c r="N3" s="15" t="inlineStr">
+      <c r="O3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">التخصص </t>
         </is>
       </c>
-      <c r="O3" s="20" t="inlineStr">
+      <c r="P3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">الهاتف </t>
         </is>
       </c>
-      <c r="P3" s="7" t="inlineStr">
+      <c r="Q3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">الجنسية </t>
         </is>
       </c>
-      <c r="Q3" s="7" t="inlineStr">
+      <c r="R3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">المؤهل </t>
         </is>
       </c>
-      <c r="R3" s="7" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">الحالة الاجتماعية</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
+      <c r="T3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">اللغة </t>
         </is>
       </c>
-      <c r="T3" s="7" t="inlineStr">
+      <c r="U3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">اسم مدير المدرسة </t>
         </is>
       </c>
-      <c r="U3" s="13" t="inlineStr">
+      <c r="V3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">الهاتف</t>
         </is>
       </c>
-      <c r="V3" s="13" t="inlineStr">
+      <c r="W3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">الجنسية </t>
         </is>
       </c>
-      <c r="W3" s="7" t="inlineStr">
+      <c r="X3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> المنهاج </t>
         </is>
       </c>
-      <c r="X3" s="7" t="inlineStr">
+      <c r="Y3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">التقويم </t>
         </is>
       </c>
-      <c r="Y3" s="19" t="inlineStr">
+      <c r="Z3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">رياضة (11)</t>
         </is>
       </c>
-      <c r="Z3" s="19" t="inlineStr">
+      <c r="AA3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">رياضة (12)</t>
         </is>
       </c>
-      <c r="AA3" s="7" t="inlineStr">
+      <c r="AB3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">الموفقة على التعيين</t>
         </is>
       </c>
-      <c r="AB3" s="21" t="inlineStr">
+      <c r="AC3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">موقع المدرسة </t>
         </is>
       </c>
-      <c r="AC3" s="21" t="inlineStr">
+      <c r="AD3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">هاتف آخر للمدرسة </t>
         </is>
       </c>
-      <c r="AD3" s="7" t="inlineStr">
+      <c r="AE3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">هاتف آخر للمدرسة </t>
         </is>
       </c>
-      <c r="AE3" s="18"/>
+      <c r="AF3" s="18"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AW3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="3">
-    <mergeCell ref="K1:T2"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="L1:U2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AC2:AD2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="34" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -938,7 +938,7 @@
     <col min="16" max="16" width="17.43" style="23" customWidth="1"/>
     <col min="17" max="17" width="12.1" style="2" customWidth="1"/>
     <col min="18" max="18" width="59.7" style="2" customWidth="1"/>
-    <col min="19" max="19" width="11.71" style="2" customWidth="1"/>
+    <col min="19" max="19" width="16.5" style="2" customWidth="1"/>
     <col min="20" max="20" width="17.8" style="2" customWidth="1"/>
     <col min="21" max="21" width="32.1" style="2" customWidth="1"/>
     <col min="22" max="22" width="15.71" style="10" customWidth="1"/>

--- a/tpl-private.xlsx
+++ b/tpl-private.xlsx
@@ -938,7 +938,7 @@
     <col min="16" max="16" width="17.43" style="23" customWidth="1"/>
     <col min="17" max="17" width="12.1" style="2" customWidth="1"/>
     <col min="18" max="18" width="59.7" style="2" customWidth="1"/>
-    <col min="19" max="19" width="16.5" style="2" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" style="2" customWidth="1"/>
     <col min="20" max="20" width="17.8" style="2" customWidth="1"/>
     <col min="21" max="21" width="32.1" style="2" customWidth="1"/>
     <col min="22" max="22" width="15.71" style="10" customWidth="1"/>
